--- a/ديمو/templates/10_مهمات_المستخلص.xlsx
+++ b/ديمو/templates/10_مهمات_المستخلص.xlsx
@@ -225,21 +225,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>المنظومة</author>
-  </authors>
-  <commentList>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>الكمية اللي اتركبت فعلاً في المستخلص ده — هي اللي بتتفوتر</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -623,7 +608,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -633,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -733,6 +717,23 @@
       <c r="A15" s="10" t="inlineStr">
         <is>
           <t>• نسخة القالب: 1.0 — لو القالب قديم السيستم هيطلب تنزيل النسخة الجديدة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>شرح الأعمدة</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>• [مهمات المستخلص] الكمية المنفذة: الكمية اللي اتركبت فعلاً في المستخلص ده — هي اللي بتتفوتر</t>
         </is>
       </c>
     </row>
@@ -747,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +775,18 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>{"مهمات المستخلص": [["1.1.7", "48 FIBER OPTIC CABLE", "KM", "2.35", ""]]}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ديمو/templates/10_مهمات_المستخلص.xlsx
+++ b/ديمو/templates/10_مهمات_المستخلص.xlsx
@@ -603,7 +603,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D3:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="لازم رقم موجب" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="D3:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="يجب إدخال رقم موجب" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -626,7 +626,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>قالب مهمات المستخلص</t>
+          <t>نموذج مهمات المستخلص</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>مين بيرفعه: الشركة المنفذة.</t>
+          <t>الجهة المسؤولة عن الرفع: المقاول (الشركة المنفذة).</t>
         </is>
       </c>
     </row>
@@ -650,21 +650,21 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>قواعد الملء</t>
+          <t>قواعد تعبئة البيانات</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>• السيستم بيقارن لكل رقم شطب: المخطط في أمر التكليف ↔ المنصرف من المخازن ↔ المنفذ التراكمي ↔ المفوتر.</t>
+          <t>• تقارن المنظومة لكل رقم شطب: الكمية المخططة في أمر التكليف ↔ المنصرف من المخازن ↔ الكمية المنفذة التراكمية ↔ الكمية المفوترة.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>• لو المنفذ أكبر من المنصرف السيستم بيعلّم الصف بالأحمر.</t>
+          <t>• إذا تجاوزت الكمية المنفذة المنصرف من المخازن تُميِّز المنظومة الصف باللون الأحمر.</t>
         </is>
       </c>
     </row>
@@ -674,49 +674,49 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>قواعد عامة لكل القوالب</t>
+          <t>قواعد عامة لجميع النماذج</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>• ما تغيّرش أسماء الشيتات ولا ترتيب الأعمدة ولا الصف التاني (اسم العمود التقني).</t>
+          <t>• لا يجوز تغيير أسماء أوراق العمل أو ترتيب الأعمدة أو الصف الثاني (الاسم التقني للعمود).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>• العمود اللي عليه * إلزامي. الأعمدة اللي فيها قائمة لازم تختار منها.</t>
+          <t>• العمود المميز بعلامة * إلزامي، ويجب الاختيار من القائمة في الأعمدة التي تتضمن قائمة اختيار.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>• الصفوف الرمادي أمثلة — امسحها قبل الرفع.</t>
+          <t>• الصفوف الرمادية أمثلة توضيحية — يرجى حذفها قبل الرفع.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>• الأرقام من غير فواصل أو عملة. التواريخ يوم/شهر/سنة.</t>
+          <t>• تُدخل الأرقام دون فواصل أو رمز عملة، والتواريخ بصيغة يوم/شهر/سنة.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>• عند الرفع السيستم بيعرض معاينة بكل صف وأخطاؤه قبل الحفظ — مفيش حاجة بتتحفظ قبل ما توافق.</t>
+          <t>• عند الرفع تعرض المنظومة نتيجة المراجعة لكل صف وأخطاءه قبل الحفظ — ولا يُحفظ أي سجل قبل «اعتماد الاستيراد».</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>• نسخة القالب: 1.0 — لو القالب قديم السيستم هيطلب تنزيل النسخة الجديدة.</t>
+          <t>• إصدار النموذج: 1.0 — إذا كان النموذج قديماً ستطلب المنظومة تحميل الإصدار الأحدث.</t>
         </is>
       </c>
     </row>
@@ -726,14 +726,14 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>شرح الأعمدة</t>
+          <t>إيضاح الأعمدة</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>• [مهمات المستخلص] الكمية المنفذة: الكمية اللي اتركبت فعلاً في المستخلص ده — هي اللي بتتفوتر</t>
+          <t>• [مهمات المستخلص] الكمية المنفذة: الكمية المركبة فعلياً في هذا المستخلص — وهي الكمية المفوترة</t>
         </is>
       </c>
     </row>

--- a/ديمو/templates/10_مهمات_المستخلص.xlsx
+++ b/ديمو/templates/10_مهمات_المستخلص.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>48 FIBER OPTIC CABLE</t>
+          <t>مثال — 48 FIBER OPTIC CABLE</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"مهمات المستخلص": [["1.1.7", "48 FIBER OPTIC CABLE", "KM", "2.35", ""]]}</t>
+          <t>{"مهمات المستخلص": [["1.1.7", "مثال — 48 FIBER OPTIC CABLE", "KM", "2.35", ""]]}</t>
         </is>
       </c>
     </row>
